--- a/08_Reports - Доклади - Berichte/Master_Financial_Timeline_Strict/master_financial_timeline_strict.xlsx
+++ b/08_Reports - Доклади - Berichte/Master_Financial_Timeline_Strict/master_financial_timeline_strict.xlsx
@@ -150,7 +150,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t/>
+          <t>73703.19</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -220,17 +220,17 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Missing strict included values for: payroll, health insurance, operating cost; 12 excluded/unknown amount rows not summed</t>
+          <t>Missing strict included values for: health insurance, operating cost; 12 excluded/unknown amount rows not summed</t>
         </is>
       </c>
     </row>
@@ -262,7 +262,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t/>
+          <t>82167.64</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -332,17 +332,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Missing strict included values for: payroll, health insurance, operating cost; 10 excluded/unknown amount rows not summed</t>
+          <t>Missing strict included values for: health insurance, operating cost; 10 excluded/unknown amount rows not summed</t>
         </is>
       </c>
     </row>
@@ -374,7 +374,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t/>
+          <t>81895.08</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -444,17 +444,17 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Missing strict included values for: payroll, health insurance, tax, operating cost; 8 excluded/unknown amount rows not summed</t>
+          <t>Missing strict included values for: health insurance, tax, operating cost; 8 excluded/unknown amount rows not summed</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t/>
+          <t>33596.07</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -780,17 +780,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Missing strict included values for: payroll, health insurance, operating cost; 8 excluded/unknown amount rows not summed</t>
+          <t>Missing strict included values for: payroll, operating cost; 8 excluded/unknown amount rows not summed</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t/>
+          <t>72130.67</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t/>
+          <t>33270.79</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -892,17 +892,17 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Missing strict included values for: payroll, health insurance, operating cost; 9 excluded/unknown amount rows not summed</t>
+          <t>Missing strict included values for: operating cost; 9 excluded/unknown amount rows not summed</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t/>
+          <t>84126.70</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t/>
+          <t>32919.94</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t/>
+          <t>7002.40</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1004,17 +1004,17 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Missing strict included values for: payroll, health insurance, tax, operating cost; 8 excluded/unknown amount rows not summed</t>
+          <t>Missing strict included values for: operating cost; 8 excluded/unknown amount rows not summed</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t/>
+          <t>39302.86</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Missing strict included values for: payroll, health insurance, operating cost; 4 excluded/unknown amount rows not summed</t>
+          <t>Missing strict included values for: payroll, operating cost; 4 excluded/unknown amount rows not summed</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t/>
+          <t>84245.80</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t/>
+          <t>40678.01</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Missing strict included values for: payroll, health insurance, operating cost; 9 excluded/unknown amount rows not summed</t>
+          <t>Missing strict included values for: operating cost; 9 excluded/unknown amount rows not summed</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t/>
+          <t>40962.45</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1340,17 +1340,17 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Missing strict included values for: payroll, health insurance, operating cost; 12 excluded/unknown amount rows not summed</t>
+          <t>Missing strict included values for: payroll, operating cost; 12 excluded/unknown amount rows not summed</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t/>
+          <t>36525.82</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1452,17 +1452,17 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Missing strict included values for: payroll, health insurance, operating cost; 9 excluded/unknown amount rows not summed</t>
+          <t>Missing strict included values for: payroll, operating cost; 9 excluded/unknown amount rows not summed</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t/>
+          <t>40514.11</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1564,17 +1564,17 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Missing strict included values for: payroll, health insurance, operating cost; 5 excluded/unknown amount rows not summed</t>
+          <t>Missing strict included values for: payroll, operating cost; 5 excluded/unknown amount rows not summed</t>
         </is>
       </c>
     </row>
@@ -1616,7 +1616,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t/>
+          <t>28247.43</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Missing strict included values for: payroll, health insurance, operating cost; 4 excluded/unknown amount rows not summed</t>
+          <t>Missing strict included values for: payroll, operating cost; 4 excluded/unknown amount rows not summed</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1748,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t/>
+          <t>4789.23</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1788,17 +1788,17 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Missing strict included values for: payroll, health insurance, tax, operating cost; 15 excluded/unknown amount rows not summed</t>
+          <t>Missing strict included values for: payroll, health insurance, operating cost; 15 excluded/unknown amount rows not summed</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1830,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t/>
+          <t>65981.53</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t/>
+          <t>28906.24</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t/>
+          <t>4518.02</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1900,17 +1900,17 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>Missing strict included values for: payroll, health insurance, tax, operating cost; 2 excluded/unknown amount rows not summed</t>
+          <t>Missing strict included values for: operating cost; 2 excluded/unknown amount rows not summed</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t/>
+          <t>51565.19</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t/>
+          <t>27082.96</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t/>
+          <t>4634.82</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -2012,17 +2012,17 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>Missing strict included values for: payroll, health insurance, tax, operating cost; 5 excluded/unknown amount rows not summed</t>
+          <t>Missing strict included values for: operating cost; 5 excluded/unknown amount rows not summed</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t/>
+          <t>34088.77</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t/>
+          <t>10334.33</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t/>
+          <t>2474.01</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2124,17 +2124,17 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>Missing strict included values for: payroll, health insurance, tax, operating cost; 9 excluded/unknown amount rows not summed</t>
+          <t>Missing strict included values for: operating cost; 9 excluded/unknown amount rows not summed</t>
         </is>
       </c>
     </row>

--- a/08_Reports - Доклади - Berichte/Master_Financial_Timeline_Strict/master_financial_timeline_strict.xlsx
+++ b/08_Reports - Доклади - Berichte/Master_Financial_Timeline_Strict/master_financial_timeline_strict.xlsx
@@ -200,12 +200,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t/>
+          <t>20898.67</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t/>
+          <t>40.00</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -215,12 +215,12 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -230,7 +230,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Missing strict included values for: health insurance, operating cost; 12 excluded/unknown amount rows not summed</t>
+          <t>Missing strict included values for: health insurance; 13 excluded/unknown amount rows not summed</t>
         </is>
       </c>
     </row>
@@ -312,12 +312,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t/>
+          <t>18617.68</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t/>
+          <t>40.00</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -332,7 +332,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -342,7 +342,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>Missing strict included values for: health insurance, operating cost; 10 excluded/unknown amount rows not summed</t>
+          <t>Missing strict included values for: health insurance; 10 excluded/unknown amount rows not summed</t>
         </is>
       </c>
     </row>
@@ -424,12 +424,12 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t/>
+          <t>101.20</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t/>
+          <t>40.00</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -444,7 +444,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -454,7 +454,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Missing strict included values for: health insurance, tax, operating cost; 8 excluded/unknown amount rows not summed</t>
+          <t>Missing strict included values for: health insurance, tax; 8 excluded/unknown amount rows not summed</t>
         </is>
       </c>
     </row>
@@ -536,12 +536,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t/>
+          <t>22955.19</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t/>
+          <t>40.00</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>Missing strict included values for: payroll, health insurance, operating cost; 8 excluded/unknown amount rows not summed</t>
+          <t>Missing strict included values for: payroll, health insurance; 8 excluded/unknown amount rows not summed</t>
         </is>
       </c>
     </row>
@@ -648,12 +648,12 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t/>
+          <t>24058.49</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t/>
+          <t>40.00</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>10</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>Missing strict included values for: payroll, health insurance, operating cost; 12 excluded/unknown amount rows not summed</t>
+          <t>Missing strict included values for: payroll, health insurance; 12 excluded/unknown amount rows not summed</t>
         </is>
       </c>
     </row>
@@ -760,12 +760,12 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t/>
+          <t>23553.36</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t/>
+          <t>40.00</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>Missing strict included values for: payroll, operating cost; 8 excluded/unknown amount rows not summed</t>
+          <t>Missing strict included values for: payroll; 8 excluded/unknown amount rows not summed</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t/>
+          <t>23067.09</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t/>
+          <t>40.00</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>Missing strict included values for: operating cost; 9 excluded/unknown amount rows not summed</t>
+          <t>9 excluded/unknown amount rows not summed</t>
         </is>
       </c>
     </row>
@@ -984,12 +984,12 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t/>
+          <t>40.46</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t/>
+          <t>40.00</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>Missing strict included values for: operating cost; 8 excluded/unknown amount rows not summed</t>
+          <t>8 excluded/unknown amount rows not summed</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t/>
+          <t>22536.76</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Missing strict included values for: payroll, operating cost; 4 excluded/unknown amount rows not summed</t>
+          <t>Missing strict included values for: payroll; 4 excluded/unknown amount rows not summed</t>
         </is>
       </c>
     </row>
@@ -1208,12 +1208,12 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t/>
+          <t>24246.81</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t/>
+          <t>40.00</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>Missing strict included values for: operating cost; 9 excluded/unknown amount rows not summed</t>
+          <t>9 excluded/unknown amount rows not summed</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t/>
+          <t>27989.44</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t/>
+          <t>40.00</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>18</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>Missing strict included values for: payroll, operating cost; 12 excluded/unknown amount rows not summed</t>
+          <t>Missing strict included values for: payroll; 12 excluded/unknown amount rows not summed</t>
         </is>
       </c>
     </row>
@@ -1432,12 +1432,12 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t/>
+          <t>23984.73</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t/>
+          <t>40.00</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>Missing strict included values for: payroll, operating cost; 9 excluded/unknown amount rows not summed</t>
+          <t>Missing strict included values for: payroll; 9 excluded/unknown amount rows not summed</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t/>
+          <t>24159.32</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>Missing strict included values for: payroll, operating cost; 5 excluded/unknown amount rows not summed</t>
+          <t>Missing strict included values for: payroll; 5 excluded/unknown amount rows not summed</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t/>
+          <t>22523.36</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>Missing strict included values for: payroll, operating cost; 4 excluded/unknown amount rows not summed</t>
+          <t>Missing strict included values for: payroll; 4 excluded/unknown amount rows not summed</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t/>
+          <t>80.00</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1783,14 +1783,14 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>MEDIUM</t>
@@ -1798,7 +1798,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Missing strict included values for: payroll, health insurance, operating cost; 15 excluded/unknown amount rows not summed</t>
+          <t>Missing strict included values for: payroll, health insurance; 16 excluded/unknown amount rows not summed</t>
         </is>
       </c>
     </row>
